--- a/artfynd/A 22399-2026 artfynd.xlsx
+++ b/artfynd/A 22399-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103410987</v>
+        <v>104157990</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530763.0926171056</v>
+        <v>530806</v>
       </c>
       <c r="R2" t="n">
-        <v>6877227.474738419</v>
+        <v>6877161</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +780,7 @@
         <v>104157987</v>
       </c>
       <c r="B3" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530732.3594250348</v>
+        <v>530732</v>
       </c>
       <c r="R3" t="n">
-        <v>6877194.804936443</v>
+        <v>6877195</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104157988</v>
+        <v>103410679</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530744.0907015201</v>
+        <v>530763</v>
       </c>
       <c r="R4" t="n">
-        <v>6877197.258368437</v>
+        <v>6877227</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,27 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104157990</v>
+        <v>104157988</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530805.5402949062</v>
+        <v>530744</v>
       </c>
       <c r="R5" t="n">
-        <v>6877160.729163365</v>
+        <v>6877197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1146,7 +1086,7 @@
         <v>129688543</v>
       </c>
       <c r="B6" t="n">
-        <v>97692</v>
+        <v>97989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22399-2026 artfynd.xlsx
+++ b/artfynd/A 22399-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157990</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157987</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103410679</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157988</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,8 +1211,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688543</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>